--- a/CQ_Generation_Framework/output/llm_input_springer_20260722_174443.xlsx
+++ b/CQ_Generation_Framework/output/llm_input_springer_20260722_174443.xlsx
@@ -32,244 +32,244 @@
     <t>scholar+publishers</t>
   </si>
   <si>
-    <t>1. What types of animal models are used in preclinical trials for radiation oncology?</t>
-  </si>
-  <si>
-    <t>2. What categories of radiation treatment protocols are defined in preclinical studies?</t>
-  </si>
-  <si>
-    <t>3. What properties characterize the subject characteristics in preclinical radiation oncology trials?</t>
-  </si>
-  <si>
-    <t>4. What relationships exist between treatment protocols and observed outcomes in radiation oncology studies?</t>
-  </si>
-  <si>
-    <t>5. What types of laboratory findings are commonly reported in preclinical trials involving radiation therapy?</t>
-  </si>
-  <si>
-    <t>6. What outcome measures are utilized to assess the efficacy of radiation treatments in preclinical studies?</t>
-  </si>
-  <si>
-    <t>7. What criteria define the experimental design of preclinical trials in radiation oncology?</t>
-  </si>
-  <si>
-    <t>8. What categories of data integration methods are applied in preclinical radiation oncology research?</t>
-  </si>
-  <si>
-    <t>9. What properties describe the data annotation process for experimental findings in radiation oncology?</t>
-  </si>
-  <si>
-    <t>10. What types of outcome measurements are used to evaluate the effectiveness of new therapies in preclinical trials?</t>
-  </si>
-  <si>
-    <t>11. What relationships exist between animal model characteristics and treatment outcomes in radiation oncology research?</t>
-  </si>
-  <si>
-    <t>12. What components constitute a comprehensive experimental design for preclinical trials in radiation oncology?</t>
-  </si>
-  <si>
-    <t>13. What types of data sharing practices are implemented among laboratories conducting preclinical trials?</t>
-  </si>
-  <si>
-    <t>14. What categories of semantic interoperability challenges are faced in integrating data from multiple studies in radiation oncology?</t>
-  </si>
-  <si>
-    <t>15. What properties define the knowledge graph structures used to represent data from preclinical trials in radiation oncology?</t>
-  </si>
-  <si>
-    <t>16. What types of observational studies are conducted to assess outcomes related to radiation therapy in animal models?</t>
-  </si>
-  <si>
-    <t>17. What criteria are used to classify different types of adverse events observed during preclinical radiation therapy trials?</t>
-  </si>
-  <si>
-    <t>18. What relationships exist between patient-derived xenograft models and their translational relevance to human cancer treatments?</t>
-  </si>
-  <si>
-    <t>19. What categories of experimental data are collected during preclinical trials involving novel radiotherapy techniques?</t>
-  </si>
-  <si>
-    <t>20. What properties describe the mechanisms underlying the abscopal effect observed in radiation oncology studies?</t>
-  </si>
-  <si>
-    <t>21. What types of biomarkers are measured as part of outcome assessments in preclinical radiation therapy research?</t>
-  </si>
-  <si>
-    <t>22. What relationships exist between immunomodulatory effects and treatment outcomes in preclinical trials with radiation therapy?</t>
-  </si>
-  <si>
-    <t>23. What criteria define the success of a treatment protocol in achieving tumor control during preclinical trials?</t>
-  </si>
-  <si>
-    <t>24. What categories of data integration techniques enhance the analysis of results from multiple preclinical studies?</t>
-  </si>
-  <si>
-    <t>25. What properties characterize the ethical considerations involved in conducting animal experiments for radiation oncology research?</t>
-  </si>
-  <si>
-    <t>26. What types of experimental designs are employed to evaluate combination therapies involving radiation and immunotherapy?</t>
-  </si>
-  <si>
-    <t>27. What relationships exist between tumor microenvironment characteristics and treatment responses observed in preclinical studies?</t>
-  </si>
-  <si>
-    <t>28. What components constitute a standardized framework for reporting outcomes from preclinical trials in radiation oncology?</t>
-  </si>
-  <si>
-    <t>29. What categories of data annotation standards are used to ensure consistency across different studies in this domain?</t>
-  </si>
-  <si>
-    <t>30. What types of statistical analyses are performed to assess the significance of findings from experimental designs in preclinical trials?</t>
-  </si>
-  <si>
-    <t>31. What properties define the criteria for selecting appropriate animal models for specific types of cancer research involving radiotherapy?</t>
-  </si>
-  <si>
-    <t>32. What relationships exist between genetic mutations and local-regional control outcomes following radiation therapy in melanoma models?</t>
-  </si>
-  <si>
-    <t>33. What categories of outcome measures are prioritized when evaluating skin toxicity associated with radiotherapy protocols?</t>
-  </si>
-  <si>
-    <t>34. What components make up a comprehensive database for storing experimental data from multiple laboratories conducting preclinical research?</t>
-  </si>
-  <si>
-    <t>35. What types of knowledge graphs can be developed to facilitate semantic interoperability among diverse datasets in radiation oncology research?</t>
-  </si>
-  <si>
-    <t>36. What criteria determine the classification of different adverse events related to photodynamic therapy combined with radiotherapy?</t>
-  </si>
-  <si>
-    <t>37. What properties characterize the methodologies used for assessing immune responses following radiotherapy treatments in animal models?</t>
-  </si>
-  <si>
-    <t>38. What relationships exist between treatment timing and efficacy when combining immunotherapy with radiotherapy protocols in preclinical studies?</t>
-  </si>
-  <si>
-    <t>39. What categories of patient-derived xenograft (PDX) models are utilized for drug testing and evaluation in radiation oncology research?</t>
-  </si>
-  <si>
-    <t>40. What components constitute a robust framework for ensuring FAIR principles are adhered to during data sharing among researchers?</t>
-  </si>
-  <si>
-    <t>41. What types of imaging techniques are employed to monitor treatment responses during preclinical radiotherapy trials?</t>
-  </si>
-  <si>
-    <t>42. What properties define the validation process for new biomarkers identified through experimental designs in cancer research?</t>
-  </si>
-  <si>
-    <t>43. What relationships exist between circulating tumor DNA levels and tumor burden during radiotherapy treatment cycles?</t>
-  </si>
-  <si>
-    <t>44. What categories of translational research strategies can be derived from findings obtained through animal models in radiation oncology?</t>
-  </si>
-  <si>
-    <t>45. What components make up an effective reporting standard for documenting laboratory findings from preclinical trials?</t>
-  </si>
-  <si>
-    <t>46. What types of statistical methods are applied to analyze outcome measures across different experimental designs?</t>
-  </si>
-  <si>
-    <t>47. What relationships exist between dose escalation protocols and observed toxicities during clinical evaluations following preclinical studies?</t>
-  </si>
-  <si>
-    <t>48. What criteria define successful integration practices for combining datasets from multiple sources within the field?</t>
-  </si>
-  <si>
-    <t>49. What categories of knowledge representation techniques support semantic interoperability across various biomedical databases?</t>
-  </si>
-  <si>
-    <t>50. What properties characterize effective communication strategies for disseminating findings from collaborative preclinical research efforts?</t>
-  </si>
-  <si>
-    <t>51. What types of experimental controls are necessary to ensure valid comparisons within treatment groups during trials?</t>
-  </si>
-  <si>
-    <t>52. What relationships exist between specific integrin expressions and treatment responses observed following combined therapies?</t>
-  </si>
-  <si>
-    <t>53. What categories of ethical guidelines must be followed when designing experiments involving animal subjects?</t>
-  </si>
-  <si>
-    <t>54. What components constitute a comprehensive assessment framework for evaluating long-term outcomes following radiotherapy?</t>
-  </si>
-  <si>
-    <t>55. What types of adverse effects should be monitored as part of toxicity assessments during combination therapy studies?</t>
-  </si>
-  <si>
-    <t>56. What properties define the structure and content requirements for annotated datasets used within this domain?</t>
-  </si>
-  <si>
-    <t>57. What relationships exist between tumor histology and response rates observed during clinical evaluations post-preclinical findings?</t>
-  </si>
-  <si>
-    <t>58. What categories of collaborative frameworks can enhance data sharing practices among researchers conducting similar studies?</t>
-  </si>
-  <si>
-    <t>59. What components make up a robust methodology for evaluating systemic effects resulting from localized radiotherapy treatments?</t>
-  </si>
-  <si>
-    <t>60. What types of computational tools can be utilized to facilitate data integration across various platforms within biomedical research?</t>
-  </si>
-  <si>
-    <t>61. What properties characterize effective training programs aimed at improving understanding among researchers regarding FAIR principles?</t>
-  </si>
-  <si>
-    <t>62. What relationships exist between patient demographics and treatment outcomes observed across different clinical trial phases?</t>
-  </si>
-  <si>
-    <t>63. What categories of molecular profiling techniques can be employed to assess tumor characteristics prior to initiating therapy?</t>
-  </si>
-  <si>
-    <t>64. What components constitute a standardized protocol for documenting laboratory findings across multiple institutions conducting similar experiments?</t>
-  </si>
-  <si>
-    <t>65. What types of safety assessments should be included as part of routine evaluations during early-phase clinical trials following promising preclinical results?</t>
-  </si>
-  <si>
-    <t>66. What properties define successful strategies for enhancing reproducibility across diverse experimental designs within this field?</t>
-  </si>
-  <si>
-    <t>67. What relationships exist between specific genetic markers and therapeutic responses observed during clinical evaluations post-preclinical investigations?</t>
-  </si>
-  <si>
-    <t>68. What categories of methodological approaches can be utilized to improve translational relevance when moving from bench to bedside applications?</t>
-  </si>
-  <si>
-    <t>69. What components make up an effective feedback mechanism for researchers involved in collaborative projects focused on shared objectives?</t>
-  </si>
-  <si>
-    <t>70. What types of observational metrics should be prioritized when assessing quality-of-life impacts resulting from various treatment modalities?</t>
-  </si>
-  <si>
-    <t>71. What properties characterize effective communication channels established among multidisciplinary teams working on complex cancer research projects?</t>
-  </si>
-  <si>
-    <t>72. What relationships exist between specific patient characteristics and their likelihood to experience adverse reactions during treatment regimens?</t>
-  </si>
-  <si>
-    <t>73. What categories define best practices for documenting experimental procedures within institutional review board submissions related to animal studies?</t>
-  </si>
-  <si>
-    <t>74 .What components constitute an effective framework for evaluating potential biases that may arise during data collection processes across different laboratories?</t>
-  </si>
-  <si>
-    <t>75 .What types of analytical methods can be employed to assess correlations between biomarker levels and clinical outcomes observed during follow-up evaluations post-treatment initiation?</t>
-  </si>
-  <si>
-    <t>76 .What properties define successful strategies aimed at ensuring ethical compliance throughout all stages involved within translational research initiatives focused on cancer therapies?</t>
-  </si>
-  <si>
-    <t>77 .What relationships exist between treatment duration and overall survival rates noted among patients participating across various trial phases involving novel interventions derived from prior investigations conducted using animal models as part thereof ?</t>
-  </si>
-  <si>
-    <t>78 .What categories encompass key performance indicators utilized when measuring success rates achieved through implementation efforts surrounding innovative therapeutic approaches developed via rigorous scientific inquiry ?</t>
-  </si>
-  <si>
-    <t>79 .What components comprise an optimal set-up necessary for conducting high-quality systematic reviews aimed at synthesizing evidence gathered through diverse lines-of-inquiry pertaining specifically towards advancements made within this rapidly evolving discipline ?</t>
-  </si>
-  <si>
-    <t>80 .What types encompass essential elements required while formulating comprehensive guidelines intended towards promoting transparency &amp; reproducibility standards adhered-to by investigators engaged-in similar lines-of-research ?</t>
+    <t>1. What types of animal models are utilized in preclinical trials for radiation oncology?</t>
+  </si>
+  <si>
+    <t>2. What categories of intervention procedures are employed in preclinical radiation studies?</t>
+  </si>
+  <si>
+    <t>3. What properties define the demographics of animals used in preclinical radiation trials?</t>
+  </si>
+  <si>
+    <t>4. What relationships exist between tumor response and radiation dosage in preclinical studies?</t>
+  </si>
+  <si>
+    <t>5. What types of clinical observations are recorded during preclinical trials in radiation oncology?</t>
+  </si>
+  <si>
+    <t>6. What properties characterize the laboratory measurements taken during preclinical trials?</t>
+  </si>
+  <si>
+    <t>7. What criteria are used to classify healthy tissue responses to radiation in animal models?</t>
+  </si>
+  <si>
+    <t>8. What types of data integration methods are applied in preclinical radiation oncology research?</t>
+  </si>
+  <si>
+    <t>9. What components constitute a comprehensive intervention procedure in preclinical trials?</t>
+  </si>
+  <si>
+    <t>10. What categories of clinical observations are relevant to assessing treatment efficacy in animal studies?</t>
+  </si>
+  <si>
+    <t>11. What properties describe the laboratory measurements related to tumor response in preclinical research?</t>
+  </si>
+  <si>
+    <t>12. What types of data standards are utilized for sharing experimental data in radiation oncology?</t>
+  </si>
+  <si>
+    <t>13. What relationships exist between intervention procedures and observed outcomes in animal models?</t>
+  </si>
+  <si>
+    <t>14. What criteria define the inclusion and exclusion of animal subjects in preclinical trials?</t>
+  </si>
+  <si>
+    <t>15. What properties characterize the tumor types studied in preclinical radiation oncology trials?</t>
+  </si>
+  <si>
+    <t>16. What categories of laboratory measurements are essential for evaluating treatment effects on tumors?</t>
+  </si>
+  <si>
+    <t>17. What types of data annotation practices are employed for experimental data in preclinical research?</t>
+  </si>
+  <si>
+    <t>18. What relationships exist between cohort descriptions and the outcomes of radiation therapy studies?</t>
+  </si>
+  <si>
+    <t>19. What properties define the variables measured during laboratory assessments in preclinical trials?</t>
+  </si>
+  <si>
+    <t>20. What categories of data integration techniques enhance the analysis of preclinical trial results?</t>
+  </si>
+  <si>
+    <t>21. What types of clinical observations indicate adverse effects on healthy tissue during radiation therapy?</t>
+  </si>
+  <si>
+    <t>22. What criteria determine the assessment endpoints for animal models undergoing radiation treatment?</t>
+  </si>
+  <si>
+    <t>23. What properties describe the characteristics of intervention procedures used in preclinical studies?</t>
+  </si>
+  <si>
+    <t>24. What relationships exist between animal demographics and their response to radiation therapy?</t>
+  </si>
+  <si>
+    <t>25. What types of laboratory measurements are critical for assessing skin toxicity in preclinical trials?</t>
+  </si>
+  <si>
+    <t>26. What categories of data sharing practices facilitate collaboration among researchers in radiation oncology?</t>
+  </si>
+  <si>
+    <t>27. What properties define the tumor microenvironment assessed during preclinical radiation studies?</t>
+  </si>
+  <si>
+    <t>28. What criteria are used to evaluate the effectiveness of different intervention procedures in trials?</t>
+  </si>
+  <si>
+    <t>29. What relationships exist between circulating tumor DNA levels and tumor response to radiation therapy?</t>
+  </si>
+  <si>
+    <t>30. What types of experimental data are collected from animal models treated with photodynamic therapy?</t>
+  </si>
+  <si>
+    <t>31. What categories of healthy tissue measurements are taken to assess radiotherapy side effects?</t>
+  </si>
+  <si>
+    <t>32. What properties characterize the cohort descriptions used in preclinical trials for data analysis?</t>
+  </si>
+  <si>
+    <t>33. What relationships exist between intervention timing and outcomes observed in animal studies?</t>
+  </si>
+  <si>
+    <t>34. What types of laboratory measurements assess immune response following radiation therapy in animals?</t>
+  </si>
+  <si>
+    <t>35. What criteria define successful tumor control following various radiation treatment modalities?</t>
+  </si>
+  <si>
+    <t>36. What properties describe the methodologies used for conducting clinical observations in trials?</t>
+  </si>
+  <si>
+    <t>37. What categories of data integration frameworks support analysis across multiple preclinical studies?</t>
+  </si>
+  <si>
+    <t>38. What types of intervention procedures are associated with enhanced tumor response rates in trials?</t>
+  </si>
+  <si>
+    <t>39. What relationships exist between specific animal demographics and treatment outcomes in studies?</t>
+  </si>
+  <si>
+    <t>40. What properties characterize the measurement techniques used to evaluate tissue damage from radiation?</t>
+  </si>
+  <si>
+    <t>41. What categories of clinical observations are necessary for understanding patient-derived xenograft responses?</t>
+  </si>
+  <si>
+    <t>42. What types of laboratory measurements are utilized to quantify tumor growth inhibition after treatment?</t>
+  </si>
+  <si>
+    <t>43. What criteria determine the standardization processes for experimental data across different studies?</t>
+  </si>
+  <si>
+    <t>44. What relationships exist between dose escalation protocols and observed toxicity levels in animal models?</t>
+  </si>
+  <si>
+    <t>45. What types of data annotation standards improve reproducibility in preclinical trial reporting?</t>
+  </si>
+  <si>
+    <t>46. What categories of intervention procedures have been shown to minimize collateral damage to healthy tissues?</t>
+  </si>
+  <si>
+    <t>47. What properties define the characteristics of cohorts selected for specific cancer type studies?</t>
+  </si>
+  <si>
+    <t>48. What relationships exist between imaging techniques and clinical observations during treatment evaluation?</t>
+  </si>
+  <si>
+    <t>49. What types of laboratory measurements inform on long-term effects post-radiation therapy?</t>
+  </si>
+  <si>
+    <t>50. What criteria guide the selection of appropriate animal models for specific cancer research questions?</t>
+  </si>
+  <si>
+    <t>51. What properties characterize the experimental designs used to assess combination therapies involving radiation?</t>
+  </si>
+  <si>
+    <t>52. What categories of clinical observations help identify biomarkers predictive of treatment response?</t>
+  </si>
+  <si>
+    <t>53. What types of data integration methods enhance comparative analyses across multiple preclinical trials?</t>
+  </si>
+  <si>
+    <t>54. What relationships exist between intervention procedures and recovery times observed post-treatment?</t>
+  </si>
+  <si>
+    <t>55. What properties define optimal conditions for conducting laboratory measurements related to toxicity assessments?</t>
+  </si>
+  <si>
+    <t>56. What criteria determine which variables should be monitored during clinical observations in trials?</t>
+  </si>
+  <si>
+    <t>57. What categories of healthy tissue assessments are necessary for evaluating radiotherapy safety profiles?</t>
+  </si>
+  <si>
+    <t>58. What types of cohort descriptions provide insights into genetic variability affecting treatment outcomes?</t>
+  </si>
+  <si>
+    <t>59. What relationships exist between experimental conditions and reproducibility rates observed across studies?</t>
+  </si>
+  <si>
+    <t>60. What properties characterize effective data sharing platforms for collaborative research efforts?</t>
+  </si>
+  <si>
+    <t>61. What categories of laboratory measurements assess cellular responses to different radiation modalities?</t>
+  </si>
+  <si>
+    <t>62. What types of intervention procedures have been associated with improved patient outcomes in clinical settings?</t>
+  </si>
+  <si>
+    <t>63. What criteria define acceptable thresholds for adverse effects observed during clinical observations?</t>
+  </si>
+  <si>
+    <t>64. What relationships exist between tumor microenvironment factors and therapeutic efficacy observed in trials?</t>
+  </si>
+  <si>
+    <t>65. What properties describe the methodologies employed for accurate measurement reporting during experiments?</t>
+  </si>
+  <si>
+    <t>66. What categories of data integration strategies facilitate real-time analysis during ongoing experiments?</t>
+  </si>
+  <si>
+    <t>67. What types of clinical observations provide evidence for the abscopal effect following localized treatments?</t>
+  </si>
+  <si>
+    <t>68. What criteria guide ethical considerations when selecting animal models for preclinical research?</t>
+  </si>
+  <si>
+    <t>69. What relationships exist between specific interventions and their impact on circulating tumor markers post-treatment?</t>
+  </si>
+  <si>
+    <t>70. What properties characterize successful collaborations among multidisciplinary teams conducting research?</t>
+  </si>
+  <si>
+    <t>71. What categories of healthy tissue evaluations inform best practices for minimizing side effects during radiotherapy?</t>
+  </si>
+  <si>
+    <t>72. What types of laboratory measurements correlate with patient-reported outcomes after treatment interventions?</t>
+  </si>
+  <si>
+    <t>73. What criteria determine which animal demographics yield the most relevant results for human applications?</t>
+  </si>
+  <si>
+    <t>74. What relationships exist between genetic profiling and observed responses to various therapeutic interventions?</t>
+  </si>
+  <si>
+    <t>75. What properties define effective communication strategies among stakeholders involved in preclinical research projects?</t>
+  </si>
+  <si>
+    <t>76. What categories of intervention procedures have shown promise in enhancing immunogenic responses alongside radiotherapy?</t>
+  </si>
+  <si>
+    <t>77. What types of clinical observations contribute to understanding long-term survivorship issues post-treatment?</t>
+  </si>
+  <si>
+    <t>78. What criteria guide the development and validation processes for new measurement tools used in experiments?</t>
+  </si>
+  <si>
+    <t>79. What relationships exist between environmental factors and their influence on experimental outcomes observed across multiple cohorts?</t>
+  </si>
+  <si>
+    <t>80. What properties characterize standardized protocols necessary for ensuring reproducibility within preclinical trial frameworks?</t>
   </si>
   <si>
     <t>Technical feasibility of [18F]FET and [18F]FAZA PET guided radiotherapy in a F98 glioblastoma rat model - Radiation Oncology</t>
